--- a/m365-productivity-blueprint/pilots/pilot_03/prototype/sandbox/P3_AutomationHost.xlsx
+++ b/m365-productivity-blueprint/pilots/pilot_03/prototype/sandbox/P3_AutomationHost.xlsx
@@ -426,7 +426,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Power Automate 'Run script from SharePoint library'가 이 파일을 대상으로 스크립트를 실행한다.</t>
+          <t>Power Automate 'Run script'(위치 OneDrive for Business)가 이 파일을 대상으로 스크립트를 실행한다. 스크립트는 본인 OneDrive '문서/Office Scripts' 폴더에 저장한다.</t>
         </is>
       </c>
     </row>
